--- a/민원 예시.xlsx
+++ b/민원 예시.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\OneDrive Backup\Minwon-Factory\Minwon_Factory\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cheonjaehyeog/Desktop/temp/Minwon_Factory/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7C072819-0B3A-4312-82F3-B605327BF57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE9C6E7-6A61-7D4D-B199-5F67B2DDCF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8925" yWindow="3540" windowWidth="21600" windowHeight="11295" xr2:uid="{9FD4BDAD-AC66-4962-B5C5-7ACA93211E64}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" xr2:uid="{9FD4BDAD-AC66-4962-B5C5-7ACA93211E64}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>이름</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,6 +67,33 @@
   </si>
   <si>
     <t>admin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>펜타플렉스 1차 수분양자입니다.
+24.6.17(월) 부산시장님 주재 주간정책회의에서 부실공사 방지를 위한 관리 철저 지시가 전부서, 전 구군에 시달되었습니다(첨부 참고)
+(시장 지시사항 제22호 172. 신축 공동주택 등 부실공사 방지를 위한 관리 철저)
+시장님께서는 최근 부실공사 사례가 증가함에 따라 시민들의 불편이 없도록 관리체계를 엄중하게 가동할 것과 공사가 마무리되는 사업들의 부실공사 방지를 위해 사전에 꼼꼼히 챙겨봐 줄 것을 당부하였습니다.
+올해 사하구 역점사업으로 지식산업센터 유치 활성화가 주요업무계획에 반영되어 있고,
+첫 번째 주자로 건설중인 펜타플렉스1차에 대해 그간 수분양자들이 수차례 부실시공 우려 민원을 제기한 바 있습니다.
+구청장님의 역점사업인 만큼 부실없는 안전한 건물로 준공되기 위해 구에서도 적극적인 관심으로 행정력을 집중할 것을 기대했고,
+시장님의 지시사항인 만큼 부실공사 방지를 위해 관리체계가 엄중히 가동될 것을 기대했습니다.
+하지만 사하구에서는 사용승인 전 현장점검을 통한 부실시공을 확인해 달라는 요청에
+감리업체의 감리결과에 이상이 없으면 현장확인 없이 승인을 한다는 원론적인 답변만 하고 있습니다.
+관련자료 정보공개에도 소극적입니다. 전형적인 탁생행정, 소극행정으로 일관하고 있습니다.
+부실시공 방지를 위해 사전에 꼼꼼하게 챙겨봐 달라는 부산시장 지시사항에도 불구하고
+여전히 현장점검 의무가 없다는 입장입니다.
+사용승인이 나면 바로 입주해야 하는 상황인데, 부실시공이 아니라면 사용승인 전에 현장점검을 안 할 이유가 없습니다.
+구청장의 역점사업인 지식산업센터
+부산시장의 부실시공 방지 지시사항
+사하구에서는 관행적인 행정은 멈춰주시고,
+수분양자들이 체감할 수 있는 적극행정을 추진해 주시기 바랍니다.
+1. 사하구는 펜타플렉스1차 수분양자들의 불편이 없도록 관리체계를 엄중하게 가동하라는 지시사항에 어떻게 조치하고 있는지 문의드립니다.
+2. 사하구는 부실공사 방지를 위해 사전에 꼼꼼히 챙겨봐 달라는 시장님 지시사항에 어떤 방식으로 꼼꼼히 챙겨보고 있는지 문의드립니다.
+부실시공으로 인한 막대한 피해는 고스란히 입주하는 수분양자에게 돌아갑니다.
+수분양자들의 피눈물같은 재산입니다.
+부디 사하구 첫 지산이 부실없는 건물이 될 수 있도록
+전 행정력을 집중해 사용승인 전 현장확인을 통해 부실시공 여부를 확인해 주시기 바랍니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -470,8 +497,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC4D766-8AF9-4BFB-8C87-463D7EE206F0}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
@@ -487,7 +514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="409.5">
+    <row r="2" spans="1:4" ht="409.6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -499,6 +526,20 @@
       </c>
       <c r="D2" s="2" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.6">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
